--- a/webcrawler/data/4_servents.xlsx
+++ b/webcrawler/data/4_servents.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="servents" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="servents" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,36 +413,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F187"/>
+  <dimension ref="A1:F193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>collectionNo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>rarity</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>className</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>name_JP</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>name_CN</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name_TW</t>
         </is>
@@ -462,63 +450,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
         <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Shielder</t>
+          <t>Alterego</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>マシュ・キリエライト</t>
+          <t>フローラ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>瑪修·基列萊特</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>瑪修．基利艾拉特</t>
-        </is>
-      </c>
+          <t>フローラ</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
         <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Saber</t>
+          <t>Shielder</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>アルトリア・ペンドラゴン〔オルタ〕</t>
+          <t>マシュ・キリエライト</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>阿爾託莉雅·潘德拉貢〔Alter〕</t>
+          <t>瑪修·基列萊特</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>阿爾托莉亞．潘德拉剛〔Alter〕</t>
+          <t>瑪修．基利艾拉特</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
         <v>4</v>
@@ -530,23 +514,23 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>アルトリア・ペンドラゴン〔リリィ〕</t>
+          <t>アルトリア・ペンドラゴン〔オルタ〕</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>阿爾託莉雅·潘德拉貢〔Lily〕</t>
+          <t>阿爾託莉雅·潘德拉貢〔Alter〕</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>阿爾托莉亞．潘德拉剛〔Lily〕</t>
+          <t>阿爾托莉亞．潘德拉剛〔Alter〕</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
@@ -558,23 +542,23 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ネロ・クラウディウス</t>
+          <t>アルトリア・ペンドラゴン〔リリィ〕</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>尼祿·克勞狄烏斯</t>
+          <t>阿爾託莉雅·潘德拉貢〔Lily〕</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>尼祿．克勞狄烏斯</t>
+          <t>阿爾托莉亞．潘德拉剛〔Lily〕</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="n">
         <v>4</v>
@@ -586,23 +570,23 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ジークフリート</t>
+          <t>ネロ・クラウディウス</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>齊格飛</t>
+          <t>尼祿·克勞狄烏斯</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>齊格飛</t>
+          <t>尼祿．克勞狄烏斯</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" t="n">
         <v>4</v>
@@ -614,51 +598,51 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>シュヴァリエ・デオン</t>
+          <t>ジークフリート</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>騎士迪昂</t>
+          <t>齊格飛</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>騎士德翁</t>
+          <t>齊格飛</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n">
         <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Archer</t>
+          <t>Saber</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>エミヤ</t>
+          <t>シュヴァリエ・デオン</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>衛宮</t>
+          <t>騎士迪昂</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Emiya</t>
+          <t>騎士德翁</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n">
         <v>4</v>
@@ -670,79 +654,79 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>アタランテ</t>
+          <t>エミヤ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>阿塔蘭忒</t>
+          <t>衛宮</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>阿塔蘭塔</t>
+          <t>Emiya</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B10" t="n">
         <v>4</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Archer</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>エリザベート・バートリー</t>
+          <t>アタランテ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>伊麗莎白·巴托里</t>
+          <t>阿塔蘭忒</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>伊莉莎白．巴托里</t>
+          <t>阿塔蘭塔</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B11" t="n">
         <v>4</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>マリー・アントワネット</t>
+          <t>エリザベート・バートリー</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>瑪麗·安託瓦內特</t>
+          <t>伊麗莎白·巴托里</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>瑪莉．安東尼</t>
+          <t>伊莉莎白．巴托里</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" t="n">
         <v>4</v>
@@ -754,51 +738,51 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>マルタ</t>
+          <t>マリー・アントワネット</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>瑪爾達</t>
+          <t>瑪麗·安託瓦內特</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>瑪爾大</t>
+          <t>瑪莉．安東尼</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B13" t="n">
         <v>4</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Assassin</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ステンノ</t>
+          <t>マルタ</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>斯忒諾</t>
+          <t>瑪爾達</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>絲忒諾</t>
+          <t>瑪爾大</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B14" t="n">
         <v>4</v>
@@ -810,51 +794,51 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>カーミラ</t>
+          <t>ステンノ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>卡米拉</t>
+          <t>斯忒諾</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>卡米拉</t>
+          <t>絲忒諾</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" t="n">
         <v>4</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Berserker</t>
+          <t>Assassin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ヘラクレス</t>
+          <t>カーミラ</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>赫拉克勒斯</t>
+          <t>卡米拉</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>赫拉克勒斯</t>
+          <t>卡米拉</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" t="n">
         <v>4</v>
@@ -866,23 +850,23 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ランスロット</t>
+          <t>ヘラクレス</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>蘭斯洛特</t>
+          <t>赫拉克勒斯</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>蘭斯洛特</t>
+          <t>赫拉克勒斯</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B17" t="n">
         <v>4</v>
@@ -894,947 +878,947 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>タマモキャット</t>
+          <t>ランスロット</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>玉藻貓</t>
+          <t>蘭斯洛特</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>玉藻貓</t>
+          <t>蘭斯洛特</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B18" t="n">
         <v>4</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Caster</t>
+          <t>Berserker</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>エリザベート・バートリー〔ハロウィン〕</t>
+          <t>タマモキャット</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>伊麗莎白·巴托里〔萬聖節〕</t>
+          <t>玉藻貓</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>伊莉莎白．巴托里〔萬聖節〕</t>
+          <t>玉藻貓</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B19" t="n">
         <v>4</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>Caster</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>アン・ボニー＆メアリー・リード</t>
+          <t>エリザベート・バートリー〔ハロウィン〕</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>安妮·伯妮＆瑪莉·瑞德</t>
+          <t>伊麗莎白·巴托里〔萬聖節〕</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>安妮．伯妮 &amp; 瑪莉．瑞德</t>
+          <t>伊莉莎白．巴托里〔萬聖節〕</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B20" t="n">
         <v>4</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Caster</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>メディア〔リリィ〕</t>
+          <t>アン・ボニー＆メアリー・リード</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>美狄亞〔Lily〕</t>
+          <t>安妮·伯妮＆瑪莉·瑞德</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>美狄亞〔Lily〕</t>
+          <t>安妮．伯妮 &amp; 瑪莉．瑞德</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B21" t="n">
         <v>4</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Archer</t>
+          <t>Caster</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>織田信長</t>
+          <t>メディア〔リリィ〕</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>織田信長</t>
+          <t>美狄亞〔Lily〕</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>織田信長</t>
+          <t>美狄亞〔Lily〕</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B22" t="n">
         <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>Archer</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>アルトリア・ペンドラゴン〔サンタオルタ〕</t>
+          <t>織田信長</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>阿爾託莉雅·潘德拉貢〔聖誕Alter〕</t>
+          <t>織田信長</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>阿爾托莉亞．潘德拉剛〔聖誕Alter〕</t>
+          <t>織田信長</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B23" t="n">
         <v>4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Caster</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ナーサリー・ライム</t>
+          <t>アルトリア・ペンドラゴン〔サンタオルタ〕</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>童謠</t>
+          <t>阿爾託莉雅·潘德拉貢〔聖誕Alter〕</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>童謠</t>
+          <t>阿爾托莉亞．潘德拉剛〔聖誕Alter〕</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B24" t="n">
         <v>4</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Caster</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>アルトリア・ペンドラゴン〔オルタ〕</t>
+          <t>ナーサリー・ライム</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>阿爾託莉雅·潘德拉貢〔Alter〕</t>
+          <t>童謠</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>阿爾托莉亞．潘德拉剛〔Alter〕</t>
+          <t>童謠</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B25" t="n">
         <v>4</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Berserker</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>フランケンシュタイン</t>
+          <t>アルトリア・ペンドラゴン〔オルタ〕</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>弗蘭肯斯坦</t>
+          <t>阿爾託莉雅·潘德拉貢〔Alter〕</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>弗蘭肯斯坦</t>
+          <t>阿爾托莉亞．潘德拉剛〔Alter〕</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B26" t="n">
         <v>4</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Berserker</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>フィン・マックール</t>
+          <t>フランケンシュタイン</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>芬恩·麥克庫爾</t>
+          <t>弗蘭肯斯坦</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>芬恩．麥克庫爾</t>
+          <t>弗蘭肯斯坦</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B27" t="n">
         <v>4</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Berserker</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ベオウルフ</t>
+          <t>フィン・マックール</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>貝奧武夫</t>
+          <t>芬恩·麥克庫爾</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>貝奧武夫</t>
+          <t>芬恩．麥克庫爾</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B28" t="n">
         <v>4</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Assassin</t>
+          <t>Berserker</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>両儀式</t>
+          <t>ベオウルフ</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>兩儀式</t>
+          <t>貝奧武夫</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>兩儀式</t>
+          <t>貝奧武夫</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B29" t="n">
         <v>4</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>Assassin</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>アストルフォ</t>
+          <t>両儀式</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>阿斯托爾福</t>
+          <t>兩儀式</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>阿斯托爾福</t>
+          <t>兩儀式</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B30" t="n">
         <v>4</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Caster</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>エレナ・ブラヴァツキー</t>
+          <t>アストルフォ</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>海倫娜·布拉瓦茨基</t>
+          <t>阿斯托爾福</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>海倫娜．布拉瓦茨基</t>
+          <t>阿斯托爾福</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saber</t>
+          <t>Caster</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ラーマ</t>
+          <t>エレナ・ブラヴァツキー</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>羅摩</t>
+          <t>海倫娜·布拉瓦茨基</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>羅摩</t>
+          <t>海倫娜．布拉瓦茨基</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Saber</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>李書文</t>
+          <t>ラーマ</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>李書文</t>
+          <t>羅摩</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>李書文</t>
+          <t>羅摩</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Caster</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>トーマス・エジソン</t>
+          <t>李書文</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>托馬斯·愛迪生</t>
+          <t>李書文</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>湯瑪斯．愛迪生</t>
+          <t>李書文</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B34" t="n">
         <v>4</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Assassin</t>
+          <t>Caster</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>エミヤ〔アサシン〕</t>
+          <t>トーマス・エジソン</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>衛宮〔Assassin〕</t>
+          <t>托馬斯·愛迪生</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Emiya〔Assassin〕</t>
+          <t>湯瑪斯．愛迪生</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B35" t="n">
         <v>4</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Caster</t>
+          <t>Assassin</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>アイリスフィール〔天の衣〕</t>
+          <t>エミヤ〔アサシン〕</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>愛麗絲菲爾〔天之衣〕</t>
+          <t>衛宮〔Assassin〕</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>愛麗絲菲爾〔天之衣〕</t>
+          <t>Emiya〔Assassin〕</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B36" t="n">
         <v>4</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>Caster</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>坂田金時</t>
+          <t>アイリスフィール〔天の衣〕</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>坂田金時</t>
+          <t>愛麗絲菲爾〔天之衣〕</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>坂田金時</t>
+          <t>愛麗絲菲爾〔天之衣〕</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B37" t="n">
         <v>4</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Berserker</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>茨木童子</t>
+          <t>坂田金時</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>茨木童子</t>
+          <t>坂田金時</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>茨木童子</t>
+          <t>坂田金時</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B38" t="n">
         <v>4</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Caster</t>
+          <t>Berserker</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ニトクリス</t>
+          <t>茨木童子</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>尼託克麗絲</t>
+          <t>茨木童子</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>尼托克里絲</t>
+          <t>茨木童子</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B39" t="n">
         <v>4</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saber</t>
+          <t>Caster</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ランスロット</t>
+          <t>ニトクリス</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>蘭斯洛特</t>
+          <t>尼託克麗絲</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>蘭斯洛特</t>
+          <t>尼托克里絲</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B40" t="n">
         <v>4</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Archer</t>
+          <t>Saber</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>トリスタン</t>
+          <t>ランスロット</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>崔斯坦</t>
+          <t>蘭斯洛特</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>崔斯坦</t>
+          <t>蘭斯洛特</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B41" t="n">
         <v>4</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saber</t>
+          <t>Archer</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ガウェイン</t>
+          <t>トリスタン</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>高文</t>
+          <t>崔斯坦</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>高文</t>
+          <t>崔斯坦</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B42" t="n">
         <v>4</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Caster</t>
+          <t>Saber</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>マリー・アントワネット</t>
+          <t>ガウェイン</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>瑪麗·安託瓦內特</t>
+          <t>高文</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>瑪莉．安東尼</t>
+          <t>高文</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B43" t="n">
         <v>4</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Archer</t>
+          <t>Caster</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>アン・ボニー＆メアリー・リード</t>
+          <t>マリー・アントワネット</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>安妮·伯妮＆瑪莉·瑞德</t>
+          <t>瑪麗·安託瓦內特</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>安妮．伯妮 &amp; 瑪莉．瑞德</t>
+          <t>瑪莉．安東尼</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B44" t="n">
         <v>4</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>Archer</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>モードレッド</t>
+          <t>アン・ボニー＆メアリー・リード</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>莫德雷德</t>
+          <t>安妮·伯妮＆瑪莉·瑞德</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>莫德雷德</t>
+          <t>安妮．伯妮 &amp; 瑪莉．瑞德</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B45" t="n">
         <v>4</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Assassin</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>スカサハ</t>
+          <t>モードレッド</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>斯卡哈</t>
+          <t>莫德雷德</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>斯卡薩哈</t>
+          <t>莫德雷德</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B46" t="n">
         <v>4</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Assassin</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>清姫</t>
+          <t>スカサハ</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>清姬</t>
+          <t>斯卡哈</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>清姬</t>
+          <t>斯卡薩哈</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B47" t="n">
         <v>4</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ruler</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>マルタ</t>
+          <t>清姫</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>瑪爾達</t>
+          <t>清姬</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>瑪爾大</t>
+          <t>清姬</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B48" t="n">
         <v>4</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Archer</t>
+          <t>Ruler</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>クロエ・フォン・アインツベルン</t>
+          <t>マルタ</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>克洛伊·馮·愛因茲貝倫</t>
+          <t>瑪爾達</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>克洛伊．馮．愛因茲貝倫</t>
+          <t>瑪爾大</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B49" t="n">
         <v>4</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Saber</t>
+          <t>Archer</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>エリザベート・バートリー〔ブレイブ〕</t>
+          <t>クロエ・フォン・アインツベルン</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>伊麗莎白·巴托里〔勇者〕</t>
+          <t>克洛伊·馮·愛因茲貝倫</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>伊莉莎白．巴托里〔Brave〕</t>
+          <t>克洛伊．馮．愛因茲貝倫</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B50" t="n">
         <v>4</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Saber</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ヴラド三世〔EXTRA〕</t>
+          <t>エリザベート・バートリー〔ブレイブ〕</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>弗拉德三世〔EXTRA〕</t>
+          <t>伊麗莎白·巴托里〔勇者〕</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>弗拉德三世〔EXTRA〕</t>
+          <t>伊莉莎白．巴托里〔Brave〕</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B51" t="n">
         <v>4</v>
@@ -1846,695 +1830,695 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ジャンヌ・ダルク・オルタ・サンタ・リリィ</t>
+          <t>ヴラド三世〔EXTRA〕</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>貞德·Alter·Santa·Lily</t>
+          <t>弗拉德三世〔EXTRA〕</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>貞德．Alter．Santa．Lily</t>
+          <t>弗拉德三世〔EXTRA〕</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B52" t="n">
         <v>4</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Caster</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ギルガメッシュ</t>
+          <t>ジャンヌ・ダルク・オルタ・サンタ・リリィ</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>吉爾伽美什</t>
+          <t>貞德·Alter·Santa·Lily</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>吉爾伽美什</t>
+          <t>貞德．Alter．Santa．Lily</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B53" t="n">
         <v>4</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Caster</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>メドゥーサ</t>
+          <t>ギルガメッシュ</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>美杜莎</t>
+          <t>吉爾伽美什</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>美杜莎</t>
+          <t>吉爾伽美什</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B54" t="n">
         <v>4</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avenger</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ゴルゴーン</t>
+          <t>メドゥーサ</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>戈耳工</t>
+          <t>美杜莎</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>戈爾貢</t>
+          <t>美杜莎</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B55" t="n">
         <v>4</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Archer</t>
+          <t>Avenger</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>エミヤ〔オルタ〕</t>
+          <t>ゴルゴーン</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>衛宮〔Alter〕</t>
+          <t>戈耳工</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Emiya〔Alter〕</t>
+          <t>戈爾貢</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B56" t="n">
         <v>4</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avenger</t>
+          <t>Archer</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ヘシアン・ロボ</t>
+          <t>エミヤ〔オルタ〕</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>黑森·羅伯</t>
+          <t>衛宮〔Alter〕</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>海森．羅伯</t>
+          <t>Emiya〔Alter〕</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B57" t="n">
         <v>4</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Assassin</t>
+          <t>Avenger</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>燕青</t>
+          <t>ヘシアン・ロボ</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>燕青</t>
+          <t>黑森·羅伯</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>燕青</t>
+          <t>海森．羅伯</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B58" t="n">
         <v>4</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Berserker</t>
+          <t>Assassin</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>茶々</t>
+          <t>燕青</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>茶茶</t>
+          <t>燕青</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>茶茶</t>
+          <t>燕青</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B59" t="n">
         <v>4</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Alterego</t>
+          <t>Berserker</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>パッションリップ</t>
+          <t>茶々</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Passionlip</t>
+          <t>茶茶</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Passionlip</t>
+          <t>茶茶</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B60" t="n">
         <v>4</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Saber</t>
+          <t>Alterego</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>鈴鹿御前</t>
+          <t>パッションリップ</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>鈴鹿御前</t>
+          <t>Passionlip</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>鈴鹿御前</t>
+          <t>Passionlip</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B61" t="n">
         <v>4</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Mooncancer</t>
+          <t>Saber</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ＢＢ</t>
+          <t>鈴鹿御前</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>鈴鹿御前</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>鈴鹿御前</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B62" t="n">
         <v>4</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Assassin</t>
+          <t>Mooncancer</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>武則天</t>
+          <t>ＢＢ</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>周照</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>武則天</t>
+          <t>BB</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B63" t="n">
         <v>4</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Berserker</t>
+          <t>Assassin</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ペンテシレイア</t>
+          <t>武則天</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>彭忒西勒亞</t>
+          <t>周照</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>彭忒西勒亞</t>
+          <t>武則天</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B64" t="n">
         <v>4</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Saber</t>
+          <t>Berserker</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>フランケンシュタイン</t>
+          <t>ペンテシレイア</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>弗蘭肯斯坦</t>
+          <t>彭忒西勒亞</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>弗蘭肯斯坦</t>
+          <t>彭忒西勒亞</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B65" t="n">
         <v>4</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Assassin</t>
+          <t>Saber</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ニトクリス</t>
+          <t>フランケンシュタイン</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>尼託克麗絲</t>
+          <t>弗蘭肯斯坦</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>尼托克里絲</t>
+          <t>弗蘭肯斯坦</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B66" t="n">
         <v>4</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Berserker</t>
+          <t>Assassin</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>織田信長</t>
+          <t>ニトクリス</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>織田信長</t>
+          <t>尼託克麗絲</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>織田信長</t>
+          <t>尼托克里絲</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B67" t="n">
         <v>4</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Archer</t>
+          <t>Berserker</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>エレナ・ブラヴァツキー</t>
+          <t>織田信長</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>海倫娜·布拉瓦茨基</t>
+          <t>織田信長</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>海倫娜．布拉瓦茨基</t>
+          <t>織田信長</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B68" t="n">
         <v>4</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Archer</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>源頼光</t>
+          <t>エレナ・ブラヴァツキー</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>源賴光</t>
+          <t>海倫娜·布拉瓦茨基</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>源賴光</t>
+          <t>海倫娜．布拉瓦茨基</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B69" t="n">
         <v>4</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>イシュタル</t>
+          <t>源頼光</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>伊什塔爾</t>
+          <t>源賴光</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>伊絲塔</t>
+          <t>源賴光</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B70" t="n">
         <v>4</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>パールヴァティー</t>
+          <t>イシュタル</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>帕爾瓦蒂</t>
+          <t>伊什塔爾</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>帕爾瓦蒂</t>
+          <t>伊絲塔</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B71" t="n">
         <v>4</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Archer</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>巴御前</t>
+          <t>パールヴァティー</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>巴御前</t>
+          <t>帕爾瓦蒂</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>巴御前</t>
+          <t>帕爾瓦蒂</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B72" t="n">
         <v>4</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Assassin</t>
+          <t>Archer</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>望月千代女</t>
+          <t>巴御前</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>望月千代女</t>
+          <t>巴御前</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>望月千代女</t>
+          <t>巴御前</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B73" t="n">
         <v>4</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Saber</t>
+          <t>Assassin</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>柳生但馬守宗矩</t>
+          <t>望月千代女</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>柳生但馬守宗矩</t>
+          <t>望月千代女</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>柳生但馬守宗矩</t>
+          <t>望月千代女</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B74" t="n">
         <v>4</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Assassin</t>
+          <t>Saber</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>加藤段蔵</t>
+          <t>柳生但馬守宗矩</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>加藤段藏</t>
+          <t>柳生但馬守宗矩</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>加藤段藏</t>
+          <t>柳生但馬守宗矩</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B75" t="n">
         <v>4</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Alterego</t>
+          <t>Assassin</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>メカエリチャン</t>
+          <t>加藤段蔵</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>機械伊麗親</t>
+          <t>加藤段藏</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>機械伊莉醬</t>
+          <t>加藤段藏</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B76" t="n">
         <v>4</v>
@@ -2546,135 +2530,135 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>メカエリチャンⅡ号機</t>
+          <t>メカエリチャン</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>機械伊麗親Ⅱ號機</t>
+          <t>機械伊麗親</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>機械伊莉醬Ⅱ號機</t>
+          <t>機械伊莉醬</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B77" t="n">
         <v>4</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Caster</t>
+          <t>Alterego</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>キルケー</t>
+          <t>メカエリチャンⅡ号機</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>喀耳刻</t>
+          <t>機械伊麗親Ⅱ號機</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>喀耳刻</t>
+          <t>機械伊莉醬Ⅱ號機</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B78" t="n">
         <v>4</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Caster</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>哪吒</t>
+          <t>キルケー</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>蓮偶</t>
+          <t>喀耳刻</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>哪吒</t>
+          <t>喀耳刻</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B79" t="n">
         <v>4</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Caster</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>シバの女王</t>
+          <t>哪吒</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>示巴女王</t>
+          <t>蓮偶</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>示巴女王</t>
+          <t>哪吒</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B80" t="n">
         <v>4</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Archer</t>
+          <t>Caster</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>アルテラ・ザ・サン〔タ〕</t>
+          <t>シバの女王</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>阿蒂拉·the·San〔ta〕</t>
+          <t>示巴女王</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>阿蒂拉．the．San〔ta〕</t>
+          <t>示巴女王</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B81" t="n">
         <v>4</v>
@@ -2686,163 +2670,163 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>浅上藤乃</t>
+          <t>アルテラ・ザ・サン〔タ〕</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>淺上藤乃</t>
+          <t>阿蒂拉·the·San〔ta〕</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>淺上藤乃</t>
+          <t>阿蒂拉．the．San〔ta〕</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B82" t="n">
         <v>4</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Berserker</t>
+          <t>Archer</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>アタランテ〔オルタ〕</t>
+          <t>浅上藤乃</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>阿塔蘭忒〔Alter〕</t>
+          <t>淺上藤乃</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>阿塔蘭塔〔Alter〕</t>
+          <t>淺上藤乃</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B83" t="n">
         <v>4</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Archer</t>
+          <t>Berserker</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ケイローン</t>
+          <t>アタランテ〔オルタ〕</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>喀戎</t>
+          <t>阿塔蘭忒〔Alter〕</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>凱隆</t>
+          <t>阿塔蘭塔〔Alter〕</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B84" t="n">
         <v>4</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Caster</t>
+          <t>Archer</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ジーク</t>
+          <t>ケイローン</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>齊格</t>
+          <t>喀戎</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>齊格</t>
+          <t>凱隆</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B85" t="n">
         <v>4</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>Caster</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>坂本龍馬</t>
+          <t>ジーク</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>坂本龍馬</t>
+          <t>齊格</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>坂本龍馬</t>
+          <t>齊格</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B86" t="n">
         <v>4</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ワルキューレ</t>
+          <t>坂本龍馬</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>瓦爾基里</t>
+          <t>坂本龍馬</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>瓦爾基麗</t>
+          <t>坂本龍馬</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B87" t="n">
         <v>4</v>
@@ -2854,639 +2838,639 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>茨木童子</t>
+          <t>ワルキューレ</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>茨木童子</t>
+          <t>瓦爾基里</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>茨木童子</t>
+          <t>瓦爾基麗</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B88" t="n">
         <v>4</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Assassin</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>牛若丸</t>
+          <t>茨木童子</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>牛若丸</t>
+          <t>茨木童子</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>牛若丸</t>
+          <t>茨木童子</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B89" t="n">
         <v>4</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Berserker</t>
+          <t>Assassin</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ジャンヌ・ダルク〔オルタ〕</t>
+          <t>牛若丸</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>貞德〔Alter〕</t>
+          <t>牛若丸</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>貞德〔Alter〕</t>
+          <t>牛若丸</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B90" t="n">
         <v>4</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Saber</t>
+          <t>Berserker</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>女王メイヴ</t>
+          <t>ジャンヌ・ダルク〔オルタ〕</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>女王梅芙</t>
+          <t>貞德〔Alter〕</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>女王梅芙</t>
+          <t>貞德〔Alter〕</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B91" t="n">
         <v>4</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Foreigner</t>
+          <t>Saber</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>謎のヒロインXX</t>
+          <t>女王メイヴ</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>謎之女主角XX</t>
+          <t>女王梅芙</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>謎之女主角XX</t>
+          <t>女王梅芙</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B92" t="n">
         <v>4</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Saber</t>
+          <t>Foreigner</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ディルムッド・オディナ</t>
+          <t>謎のヒロインXX</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>迪爾姆德·奧迪那</t>
+          <t>謎之女主角XX</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>迪爾姆德．奧德利暗</t>
+          <t>謎之女主角XX</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B93" t="n">
         <v>4</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Caster</t>
+          <t>Saber</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>酒呑童子</t>
+          <t>ディルムッド・オディナ</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>酒吞童子</t>
+          <t>迪爾姆德·奧迪那</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>酒吞童子</t>
+          <t>迪爾姆德．奧德利暗</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B94" t="n">
         <v>4</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Saber</t>
+          <t>Caster</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>蘭陵王</t>
+          <t>酒呑童子</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>蘭陵王</t>
+          <t>酒吞童子</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>蘭陵王</t>
+          <t>酒吞童子</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B95" t="n">
         <v>4</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Saber</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>秦良玉</t>
+          <t>蘭陵王</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>忠貞</t>
+          <t>蘭陵王</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>秦良玉</t>
+          <t>蘭陵王</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B96" t="n">
         <v>4</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Assassin</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>虞美人</t>
+          <t>秦良玉</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>雛罌</t>
+          <t>忠貞</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>虞美人</t>
+          <t>秦良玉</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B97" t="n">
         <v>4</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ruler</t>
+          <t>Assassin</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ケツァル・コアトル〔サンバ／サンタ〕</t>
+          <t>虞美人</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>魁札爾·科亞特爾〔桑巴／聖誕〕</t>
+          <t>雛罌</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>魁札爾．科亞特爾〔森巴／聖誕〕</t>
+          <t>虞美人</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B98" t="n">
         <v>4</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Caster</t>
+          <t>Ruler</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>美遊・エーデルフェルト</t>
+          <t>ケツァル・コアトル〔サンバ／サンタ〕</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>美遊·艾德費爾特</t>
+          <t>魁札爾·科亞特爾〔桑巴／聖誕〕</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>美遊．艾蒂菲爾特</t>
+          <t>魁札爾．科亞特爾〔森巴／聖誕〕</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B99" t="n">
         <v>4</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ruler</t>
+          <t>Caster</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>アストライア</t>
+          <t>美遊・エーデルフェルト</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>阿斯特賴亞</t>
+          <t>美遊·艾德費爾特</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>阿斯特蕾亞</t>
+          <t>美遊．艾蒂菲爾特</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B100" t="n">
         <v>4</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Assassin</t>
+          <t>Ruler</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>グレイ</t>
+          <t>アストライア</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>格蕾</t>
+          <t>阿斯特賴亞</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>格蕾</t>
+          <t>阿斯特蕾亞</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B101" t="n">
         <v>4</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Saber</t>
+          <t>Assassin</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ラクシュミー・バーイー</t>
+          <t>グレイ</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>拉克什米·芭伊</t>
+          <t>格蕾</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>拉克西米．芭伊</t>
+          <t>格蕾</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B102" t="n">
         <v>4</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Archer</t>
+          <t>Saber</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>アシュヴァッターマン</t>
+          <t>ラクシュミー・バーイー</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>馬嘶</t>
+          <t>拉克什米·芭伊</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>馬嘶</t>
+          <t>拉克西米．芭伊</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B103" t="n">
         <v>4</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Archer</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>長尾景虎</t>
+          <t>アシュヴァッターマン</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>長尾景虎</t>
+          <t>馬嘶</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>長尾景虎</t>
+          <t>馬嘶</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B104" t="n">
         <v>4</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Archer</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>刑部姫</t>
+          <t>長尾景虎</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>刑部姬</t>
+          <t>長尾景虎</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>刑部姬</t>
+          <t>長尾景虎</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B105" t="n">
         <v>4</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>Archer</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>カーミラ</t>
+          <t>刑部姫</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>卡米拉</t>
+          <t>刑部姬</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>卡米拉</t>
+          <t>刑部姬</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B106" t="n">
         <v>4</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Saber</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>葛飾北斎</t>
+          <t>カーミラ</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>葛飾北齋</t>
+          <t>卡米拉</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>葛飾北齋</t>
+          <t>卡米拉</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B107" t="n">
         <v>4</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Saber</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>謎のアルターエゴ・Λ</t>
+          <t>葛飾北斎</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>謎之Alterego·Λ</t>
+          <t>葛飾北齋</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>謎之Alterego．Λ</t>
+          <t>葛飾北齋</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B108" t="n">
         <v>4</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Assassin</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>沖田総司</t>
+          <t>謎のアルターエゴ・Λ</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>沖田總司</t>
+          <t>謎之Alterego·Λ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>沖田總司</t>
+          <t>謎之Alterego．Λ</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B109" t="n">
         <v>4</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Archer</t>
+          <t>Assassin</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>カラミティ・ジェーン</t>
+          <t>沖田総司</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>災星簡</t>
+          <t>沖田總司</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>災星簡</t>
+          <t>沖田總司</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B110" t="n">
         <v>4</v>
@@ -3498,275 +3482,275 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ナイチンゲール〔サンタ〕</t>
+          <t>カラミティ・ジェーン</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>南丁格爾〔聖誕〕</t>
+          <t>災星簡</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>南丁格爾〔Santa〕</t>
+          <t>災星簡</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B111" t="n">
         <v>4</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Archer</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>カイニス</t>
+          <t>ナイチンゲール〔サンタ〕</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>凱妮斯</t>
+          <t>南丁格爾〔聖誕〕</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>凱妮絲</t>
+          <t>南丁格爾〔Santa〕</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B112" t="n">
         <v>4</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Berserker</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>鬼女紅葉</t>
+          <t>カイニス</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>鬼女紅葉</t>
+          <t>凱妮斯</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>鬼女紅葉</t>
+          <t>凱妮絲</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B113" t="n">
         <v>4</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Berserker</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>宇津見エリセ</t>
+          <t>鬼女紅葉</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>宇津見繪里瀨</t>
+          <t>鬼女紅葉</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>宇津見繪里世</t>
+          <t>鬼女紅葉</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B114" t="n">
         <v>4</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Archer</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>イリヤスフィール・フォン・アインツベルン</t>
+          <t>宇津見エリセ</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>伊莉雅絲菲爾·馮·愛因茲貝倫</t>
+          <t>宇津見繪里瀨</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>伊莉雅絲菲爾．馮．愛因茲貝倫</t>
+          <t>宇津見繪里世</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B115" t="n">
         <v>4</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Berserker</t>
+          <t>Archer</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ブリュンヒルデ</t>
+          <t>イリヤスフィール・フォン・アインツベルン</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>布倫希爾德</t>
+          <t>伊莉雅絲菲爾·馮·愛因茲貝倫</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>布倫希爾德</t>
+          <t>伊莉雅絲菲爾．馮．愛因茲貝倫</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B116" t="n">
         <v>4</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Berserker</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>虞美人</t>
+          <t>ブリュンヒルデ</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>雛罌</t>
+          <t>布倫希爾德</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>虞美人</t>
+          <t>布倫希爾德</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B117" t="n">
         <v>4</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Saber</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>巴御前</t>
+          <t>虞美人</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>巴御前</t>
+          <t>雛罌</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>巴御前</t>
+          <t>虞美人</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B118" t="n">
         <v>4</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>Saber</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>紫式部</t>
+          <t>巴御前</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>紫式部</t>
+          <t>巴御前</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>紫式部</t>
+          <t>巴御前</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B119" t="n">
         <v>4</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Saber</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>斎藤一</t>
+          <t>紫式部</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>齋藤一</t>
+          <t>紫式部</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>齋藤一</t>
+          <t>紫式部</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B120" t="n">
         <v>4</v>
@@ -3778,23 +3762,23 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>渡辺綱</t>
+          <t>斎藤一</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>渡邊綱</t>
+          <t>齋藤一</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>渡邊綱</t>
+          <t>齋藤一</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B121" t="n">
         <v>4</v>
@@ -3806,751 +3790,751 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>カルナ〔サンタ〕</t>
+          <t>渡辺綱</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>迦爾納〔聖誕〕</t>
+          <t>渡邊綱</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>迦爾納〔Santa〕</t>
+          <t>渡邊綱</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B122" t="n">
         <v>4</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Assassin</t>
+          <t>Saber</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>鬼一法眼</t>
+          <t>カルナ〔サンタ〕</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>鬼一法眼</t>
+          <t>迦爾納〔聖誕〕</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>鬼一法眼</t>
+          <t>迦爾納〔Santa〕</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B123" t="n">
         <v>4</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Foreigner</t>
+          <t>Assassin</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>謎のアイドルX〔オルタ〕</t>
+          <t>鬼一法眼</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>謎之偶像X〔Alter〕</t>
+          <t>鬼一法眼</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>謎之偶像X〔Alter〕</t>
+          <t>鬼一法眼</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B124" t="n">
         <v>4</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Saber</t>
+          <t>Foreigner</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>バーゲスト</t>
+          <t>謎のアイドルX〔オルタ〕</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>巴格斯特</t>
+          <t>謎之偶像X〔Alter〕</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>巴格斯特</t>
+          <t>謎之偶像X〔Alter〕</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B125" t="n">
         <v>4</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Archer</t>
+          <t>Saber</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>バーヴァン・シー</t>
+          <t>バーゲスト</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>芭萬·希</t>
+          <t>巴格斯特</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>芭班．希</t>
+          <t>巴格斯特</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B126" t="n">
         <v>4</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Archer</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>パーシヴァル</t>
+          <t>バーヴァン・シー</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>珀西瓦爾</t>
+          <t>芭萬·希</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>帕西瓦爾</t>
+          <t>芭班．希</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B127" t="n">
         <v>4</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ハベトロット</t>
+          <t>パーシヴァル</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>哈貝特洛特</t>
+          <t>珀西瓦爾</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>哈貝特洛特</t>
+          <t>帕西瓦爾</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B128" t="n">
         <v>4</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Archer</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>アナスタシア＆ヴィイ</t>
+          <t>ハベトロット</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>阿納斯塔西婭＆維</t>
+          <t>哈貝特洛特</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>安娜塔西亞＆Viy</t>
+          <t>哈貝特洛特</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B129" t="n">
         <v>4</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Caster</t>
+          <t>Archer</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>シャルロット・コルデー</t>
+          <t>アナスタシア＆ヴィイ</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>夏洛特·科黛</t>
+          <t>阿納斯塔西婭＆維</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>夏洛特．科黛</t>
+          <t>安娜塔西亞＆Viy</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B130" t="n">
         <v>4</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ruler</t>
+          <t>Caster</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>レオナルド・ダ・ヴィンチ</t>
+          <t>シャルロット・コルデー</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>萊昂納多·達·芬奇</t>
+          <t>夏洛特·科黛</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>李奧納多．達．文西</t>
+          <t>夏洛特．科黛</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B131" t="n">
         <v>4</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>Ruler</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>カイニス</t>
+          <t>レオナルド・ダ・ヴィンチ</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>凱妮斯</t>
+          <t>萊昂納多·達·芬奇</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>凱妮絲</t>
+          <t>李奧納多．達．文西</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B132" t="n">
         <v>4</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Berserker</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>清少納言</t>
+          <t>カイニス</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>清少納言</t>
+          <t>凱妮斯</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>清少納言</t>
+          <t>凱妮絲</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B133" t="n">
         <v>4</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Archer</t>
+          <t>Berserker</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ゼノビア</t>
+          <t>清少納言</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>芝諾比阿</t>
+          <t>清少納言</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>潔諾比亞</t>
+          <t>清少納言</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B134" t="n">
         <v>4</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>Archer</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>エリザベート・バートリー〔シンデレラ〕</t>
+          <t>ゼノビア</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>伊麗莎白·巴托里〔灰姑娘〕</t>
+          <t>芝諾比阿</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>伊莉莎白．巴托里〔Cinderella〕</t>
+          <t>潔諾比亞</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B135" t="n">
         <v>4</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avenger</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>謎の蘭丸X</t>
+          <t>エリザベート・バートリー〔シンデレラ〕</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>謎之蘭丸X</t>
+          <t>伊麗莎白·巴托里〔灰姑娘〕</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>謎之蘭丸X</t>
+          <t>伊莉莎白．巴托里〔Cinderella〕</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B136" t="n">
         <v>4</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Caster</t>
+          <t>Avenger</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>マルタ〔サンタ〕</t>
+          <t>謎の蘭丸X</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>瑪爾達〔聖誕〕</t>
+          <t>謎之蘭丸X</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>瑪爾大〔Santa〕</t>
+          <t>謎之蘭丸X</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B137" t="n">
         <v>4</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>Caster</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ドブルイニャ・ニキチッチ</t>
+          <t>マルタ〔サンタ〕</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>多佈雷尼亞·尼基季奇</t>
+          <t>瑪爾達〔聖誕〕</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>多布雷尼亞．尼基季奇</t>
+          <t>瑪爾大〔Santa〕</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B138" t="n">
         <v>4</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Pretender</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>ヘファイスティオン</t>
+          <t>ドブルイニャ・ニキチッチ</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>赫費斯提翁</t>
+          <t>多佈雷尼亞·尼基季奇</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>赫費斯提翁</t>
+          <t>多布雷尼亞．尼基季奇</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B139" t="n">
         <v>4</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Alterego</t>
+          <t>Pretender</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>太歳星君</t>
+          <t>ヘファイスティオン</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>太歲星君</t>
+          <t>赫費斯提翁</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>太歲星君</t>
+          <t>赫費斯提翁</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B140" t="n">
         <v>4</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Caster</t>
+          <t>Alterego</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>大黒天</t>
+          <t>太歳星君</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>大黑天</t>
+          <t>太歲星君</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>大黑天</t>
+          <t>太歲星君</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B141" t="n">
         <v>4</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Saber</t>
+          <t>Caster</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>ローラン</t>
+          <t>大黒天</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>羅蘭</t>
+          <t>大黑天</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>羅蘭</t>
+          <t>大黑天</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B142" t="n">
         <v>4</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Berserker</t>
+          <t>Saber</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>クリームヒルト</t>
+          <t>ローラン</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>克里姆希爾德</t>
+          <t>羅蘭</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>克琳希德</t>
+          <t>羅蘭</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B143" t="n">
         <v>4</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Berserker</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ドン・キホーテ</t>
+          <t>クリームヒルト</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>堂·吉訶德</t>
+          <t>克里姆希爾德</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>唐吉訶德</t>
+          <t>克琳希德</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B144" t="n">
         <v>4</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Saber</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ガレス</t>
+          <t>ドン・キホーテ</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>加雷斯</t>
+          <t>堂·吉訶德</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>加雷斯</t>
+          <t>唐吉訶德</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B145" t="n">
         <v>4</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avenger</t>
+          <t>Saber</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>宇津見エリセ</t>
+          <t>ガレス</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>宇津見繪里瀨</t>
+          <t>加雷斯</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>宇津見繪里世</t>
+          <t>加雷斯</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B146" t="n">
         <v>4</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Caster</t>
+          <t>Avenger</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>武則天</t>
+          <t>宇津見エリセ</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>周照</t>
+          <t>宇津見繪里瀨</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>武則天</t>
+          <t>宇津見繪里世</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B147" t="n">
         <v>4</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Assassin</t>
+          <t>Caster</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>スルーズ</t>
+          <t>武則天</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>斯露德</t>
+          <t>周照</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>斯露德</t>
+          <t>武則天</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B148" t="n">
         <v>4</v>
@@ -4562,23 +4546,23 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ヒルド</t>
+          <t>スルーズ</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>希露德</t>
+          <t>斯露德</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>希露德</t>
+          <t>斯露德</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B149" t="n">
         <v>4</v>
@@ -4590,135 +4574,135 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>オルトリンデ</t>
+          <t>ヒルド</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>奧特琳德</t>
+          <t>希露德</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>奧特琳德</t>
+          <t>希露德</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B150" t="n">
         <v>4</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Saber</t>
+          <t>Assassin</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>山南敬助</t>
+          <t>オルトリンデ</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>山南敬助</t>
+          <t>奧特琳德</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>山南敬助</t>
+          <t>奧特琳德</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B151" t="n">
         <v>4</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Ruler</t>
+          <t>Saber</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>壱与</t>
+          <t>山南敬助</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>壹與</t>
+          <t>山南敬助</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>臺與</t>
+          <t>山南敬助</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B152" t="n">
         <v>4</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>Ruler</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>黄飛虎</t>
+          <t>壱与</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>黃飛虎</t>
+          <t>壹與</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>黃飛虎</t>
+          <t>臺與</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B153" t="n">
         <v>4</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Pretender</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>九紋竜エリザ</t>
+          <t>黄飛虎</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>九紋龍伊麗莎</t>
+          <t>黃飛虎</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>九紋龍伊莉莎</t>
+          <t>黃飛虎</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B154" t="n">
         <v>4</v>
@@ -4730,587 +4714,611 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>テノチティトラン</t>
+          <t>九紋竜エリザ</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>特諾奇蒂特蘭</t>
+          <t>九紋龍伊麗莎</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>特諾奇提特蘭</t>
+          <t>九紋龍伊莉莎</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="B155" t="n">
         <v>4</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Assassin</t>
+          <t>Pretender</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>ロクスタ</t>
+          <t>テノチティトラン</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>洛庫斯塔</t>
+          <t>特諾奇蒂特蘭</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>洛庫斯塔</t>
+          <t>特諾奇提特蘭</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B156" t="n">
         <v>4</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Saber</t>
+          <t>Assassin</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>セタンタ</t>
+          <t>ロクスタ</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>瑟坦特</t>
+          <t>洛庫斯塔</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>瑟坦特</t>
+          <t>洛庫斯塔</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B157" t="n">
         <v>4</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Berserker</t>
+          <t>Saber</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ドゥリーヨダナ</t>
+          <t>セタンタ</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>難敵</t>
+          <t>瑟坦特</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>難敵</t>
+          <t>瑟坦特</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B158" t="n">
         <v>4</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>Berserker</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>鈴鹿御前〔サマバケ〕</t>
+          <t>ドゥリーヨダナ</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>鈴鹿御前〔暑假〕</t>
+          <t>難敵</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>鈴鹿御前〔暑假〕</t>
+          <t>難敵</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B159" t="n">
         <v>4</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avenger</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>クロエ・フォン・アインツベルン</t>
+          <t>鈴鹿御前〔サマバケ〕</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>克洛伊·馮·愛因茲貝倫</t>
+          <t>鈴鹿御前〔暑假〕</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>克洛伊．馮．愛因茲貝倫</t>
+          <t>鈴鹿御前〔暑假〕</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B160" t="n">
         <v>4</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Foreigner</t>
+          <t>Avenger</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>ノクナレア・ヤラアーンドゥ</t>
+          <t>クロエ・フォン・アインツベルン</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>諾克娜蕾·雅蘭杜</t>
+          <t>克洛伊·馮·愛因茲貝倫</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>諾克娜蕾雅．雅蘭杜</t>
+          <t>克洛伊．馮．愛因茲貝倫</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B161" t="n">
         <v>4</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Archer</t>
+          <t>Foreigner</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>ＵＤＫ－バーゲスト</t>
+          <t>ノクナレア・ヤラアーンドゥ</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>ＵＤＫ－巴格斯特</t>
+          <t>諾克娜蕾·雅蘭杜</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>ＵＤＫ－巴格斯特</t>
+          <t>諾克娜蕾雅．雅蘭杜</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B162" t="n">
         <v>4</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Pretender</t>
+          <t>Archer</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>ケット・クー・ミコケル</t>
+          <t>ＵＤＫ－バーゲスト</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>凱特·庫·米可科爾</t>
+          <t>ＵＤＫ－巴格斯特</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>凱特．庫．米可科爾</t>
+          <t>ＵＤＫ－巴格斯特</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B163" t="n">
         <v>4</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Berserker</t>
+          <t>Pretender</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>永倉新八</t>
+          <t>ケット・クー・ミコケル</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>永倉新八</t>
+          <t>凱特·庫·米可科爾</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>永倉新八</t>
+          <t>凱特．庫．米可科爾</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B164" t="n">
         <v>4</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Archer</t>
+          <t>Berserker</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>雑賀孫一</t>
+          <t>永倉新八</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>雜賀孫一</t>
+          <t>永倉新八</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>雜賀孫一</t>
+          <t>永倉新八</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B165" t="n">
         <v>4</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>Archer</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>ネモ〔サンタ〕</t>
+          <t>雑賀孫一</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>尼莫〔聖誕〕</t>
+          <t>雜賀孫一</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>尼莫〔Santa〕</t>
+          <t>雜賀孫一</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B166" t="n">
         <v>4</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Caster</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>由井正雪</t>
+          <t>ネモ〔サンタ〕</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>由井正雪</t>
+          <t>尼莫〔聖誕〕</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>由井正雪</t>
+          <t>尼莫〔Santa〕</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B167" t="n">
         <v>4</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Saber</t>
+          <t>Caster</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>宮本伊織</t>
+          <t>由井正雪</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>宮本伊織</t>
+          <t>由井正雪</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>宮本伊織</t>
+          <t>由井正雪</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B168" t="n">
         <v>4</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Assassin</t>
+          <t>Saber</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>耀星のハサン</t>
+          <t>宮本伊織</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>耀星哈桑</t>
+          <t>宮本伊織</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>耀星的哈桑</t>
+          <t>宮本伊織</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B169" t="n">
         <v>4</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Pretender</t>
+          <t>Assassin</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>アレッサンドロ・ディ・カリオストロ</t>
+          <t>耀星のハサン</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>亞歷山德羅·迪·卡利奧斯特羅</t>
+          <t>耀星哈桑</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>亞歷山德羅．迪．卡廖斯特羅</t>
+          <t>耀星的哈桑</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B170" t="n">
         <v>4</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Berserker</t>
+          <t>Pretender</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>静希草十郎</t>
+          <t>アレッサンドロ・ディ・カリオストロ</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>靜希草十郎</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr"/>
+          <t>亞歷山德羅·迪·卡利奧斯特羅</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>亞歷山德羅．迪．卡廖斯特羅</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B171" t="n">
         <v>4</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Berserker</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ドブルイニャ・ニキチッチ</t>
+          <t>静希草十郎</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>多佈雷尼亞·尼基季奇</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr"/>
+          <t>靜希草十郎</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>靜希草十郎</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B172" t="n">
         <v>4</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avenger</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>徐福</t>
+          <t>ドブルイニャ・ニキチッチ</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>方巿</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr"/>
+          <t>多佈雷尼亞·尼基季奇</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>多布雷尼亞．尼基季奇</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B173" t="n">
         <v>4</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Mooncancer</t>
+          <t>Avenger</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>テノチティトラン</t>
+          <t>徐福</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>特諾奇蒂特蘭</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr"/>
+          <t>方巿</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>徐福</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B174" t="n">
         <v>4</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Foreigner</t>
+          <t>Mooncancer</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>謎のヒロインXX〔オルタ〕</t>
+          <t>テノチティトラン</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>謎之女主角XX〔Alter〕</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr"/>
+          <t>特諾奇蒂特蘭</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>特諾奇提特蘭</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B175" t="n">
         <v>4</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Mooncancer</t>
+          <t>Foreigner</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>岸波白野</t>
+          <t>謎のヒロインXX〔オルタ〕</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>岸波白野</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr"/>
+          <t>謎之女主角XX〔Alter〕</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>謎之女主角XX〔Alter〕</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B176" t="n">
         <v>4</v>
@@ -5330,131 +5338,151 @@
           <t>岸波白野</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>岸波白野</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B177" t="n">
         <v>4</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Mooncancer</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ヴァン・ゴッホ〔マイナー〕</t>
+          <t>岸波白野</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>梵高〔礦工〕</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr"/>
+          <t>岸波白野</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>岸波白野</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B178" t="n">
         <v>4</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Pretender</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>アビゲイル・ウィリアムズ〔サンタ〕</t>
+          <t>ヴァン・ゴッホ〔マイナー〕</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>阿比蓋爾·威廉姆斯〔聖誕〕</t>
+          <t>梵高〔礦工〕</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B179" t="n">
         <v>4</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Saber</t>
+          <t>Pretender</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>黒姫</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr"/>
+          <t>アビゲイル・ウィリアムズ〔サンタ〕</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>阿比蓋爾·威廉姆斯〔聖誕〕</t>
+        </is>
+      </c>
       <c r="F179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B180" t="n">
         <v>4</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Saber</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>アショカ王</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr"/>
+          <t>黒姫</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>黑姬</t>
+        </is>
+      </c>
       <c r="F180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="B181" t="n">
         <v>4</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Rider</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>クリームヒルト</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr"/>
+          <t>アショカ王</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>阿育王</t>
+        </is>
+      </c>
       <c r="F181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B182" t="n">
         <v>4</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Berserker</t>
+          <t>Rider</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>呼延灼</t>
+          <t>クリームヒルト</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -5462,19 +5490,19 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B183" t="n">
         <v>4</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Berserker</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>美遊・エーデルフェルト</t>
+          <t>呼延灼</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -5482,19 +5510,19 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B184" t="n">
         <v>4</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Alterego</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>ジュネス・クレーン</t>
+          <t>美遊・エーデルフェルト</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -5502,19 +5530,19 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B185" t="n">
         <v>4</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avenger</t>
+          <t>Alterego</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>藤堂平助</t>
+          <t>ジュネス・クレーン</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -5522,19 +5550,19 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B186" t="n">
         <v>4</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Lancer</t>
+          <t>Avenger</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>原田左之助</t>
+          <t>藤堂平助</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -5542,23 +5570,143 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B187" t="n">
         <v>4</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Avenger</t>
+          <t>Lancer</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>終わりのエリザベート</t>
+          <t>原田左之助</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>458</v>
+      </c>
+      <c r="B188" t="n">
+        <v>4</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Avenger</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>終わりのエリザベート</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>463</v>
+      </c>
+      <c r="B189" t="n">
+        <v>4</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Assassin</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>蛇女房</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>464</v>
+      </c>
+      <c r="B190" t="n">
+        <v>4</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Alterego</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>フローラ</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>468</v>
+      </c>
+      <c r="B191" t="n">
+        <v>4</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Rider</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>ヒッポリュテ</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>472</v>
+      </c>
+      <c r="B192" t="n">
+        <v>4</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Saber</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>グレイ・リリィ</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>473</v>
+      </c>
+      <c r="B193" t="n">
+        <v>4</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Lancer</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>グレイ・リリィ</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/webcrawler/data/4_servents.xlsx
+++ b/webcrawler/data/4_servents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F193"/>
+  <dimension ref="A1:F196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5394,7 +5394,11 @@
           <t>梵高〔礦工〕</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>梵谷〔礦工〕</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -5418,7 +5422,11 @@
           <t>阿比蓋爾·威廉姆斯〔聖誕〕</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>艾比蓋兒．威廉斯〔Santa〕</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -5485,7 +5493,11 @@
           <t>クリームヒルト</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>克里姆希爾德</t>
+        </is>
+      </c>
       <c r="F182" t="inlineStr"/>
     </row>
     <row r="183">
@@ -5505,7 +5517,11 @@
           <t>呼延灼</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>吾綽</t>
+        </is>
+      </c>
       <c r="F183" t="inlineStr"/>
     </row>
     <row r="184">
@@ -5525,7 +5541,11 @@
           <t>美遊・エーデルフェルト</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>美遊·艾德費爾特</t>
+        </is>
+      </c>
       <c r="F184" t="inlineStr"/>
     </row>
     <row r="185">
@@ -5545,7 +5565,11 @@
           <t>ジュネス・クレーン</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>熱內斯·克萊恩</t>
+        </is>
+      </c>
       <c r="F185" t="inlineStr"/>
     </row>
     <row r="186">
@@ -5707,6 +5731,66 @@
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>477</v>
+      </c>
+      <c r="B194" t="n">
+        <v>4</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Caster</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>ビショーネ</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>480</v>
+      </c>
+      <c r="B195" t="n">
+        <v>4</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Archer</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>小野小町</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>481</v>
+      </c>
+      <c r="B196" t="n">
+        <v>4</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Pretender</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>ハベトロット</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
